--- a/research/brics_universities/output/BRICS_universities_indonesia.xlsx
+++ b/research/brics_universities/output/BRICS_universities_indonesia.xlsx
@@ -558,10 +558,10 @@
         <v>101</v>
       </c>
       <c r="G5" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H5" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -1487,7 +1487,8 @@
           <t>• ВНИМАНИЕ: домен surya.ac.id сейчас (окт. 2026) показывает сайт «Surya Academy» (математика, бизнес, экономика) без контактов и руководства; старые страницы Surya University (в т.ч. о SS-1) дают 404 — статус вуза (ребрендинг/реорганизация) неясен
 • Ректор не подтверждён официальным источником 2025–2026; в Википедии указаны Lindawati, Ph.D. (id.wiki) и Prof. Yohanes Surya (en.wiki) — перед рассылкой уточнить
 • SS-1 (1U, APRS) — первый студенческий спутник Индонезии: запуск 26.11.2022 (SpaceX CRS-26 к МКС), отделение от МКС 06.01.2023 по программе KiboCUBE, сошёл с орбиты 11.05.2023
-• Email/телефон на текущем сайте не опубликованы — нужен поиск контакта (например, через команду SS-1 или фонд Surya Institute)</t>
+• Email/телефон на текущем сайте не опубликованы — нужен поиск контакта (например, через команду SS-1 или фонд Surya Institute)
+• Перепроверка: Сайт surya.ac.id повторно проверен 04.10.2026: это «Surya Academy» без руководства и контактов; данные не изменены, статус вуза не прояснён</t>
         </is>
       </c>
       <c r="AG5" s="4" t="inlineStr">
@@ -1818,11 +1819,12 @@
       </c>
       <c r="AF7" s="4" t="inlineStr">
         <is>
-          <t>• Сайт itera.ac.id и поддомены блокируют доступ (403 / Cloudflare-проверка) — контакты (pusat@itera.ac.id, iio@itera.ac.id, телефон) взяты только из поисковой выдачи, не со страницы; перепроверить
-• Ректор проф. Эльфахми избран 20.05.2026, вступил в должность 30.06.2026 (срок 2026–2030), сменив проф. I Nyoman Pugeg Aryantha
+          <t>• Сайт itera.ac.id и поддомены (pmb., kemahasiswaan., at., mfi.) блокируют доступ (403 / Cloudflare, повторно 04.10.2026) — контакты (pusat@itera.ac.id, iio@itera.ac.id, +62 721 8030188; PR-служба humas@itera.ac.id) взяты из поисковой выдачи официальных страниц, не открыты; перепроверить
+• Ректор проф. Эльфахми избран 20.05.2026, вступил в должность 30.06.2026 (срок 2026–2030), сменив проф. I Nyoman Pugeg Aryantha — по официальной новости ITB
 • Город: кампус в округе Южный Лампунг рядом с Бандар-Лампунгом
 • Собственных спутников нет; есть станция приёма метеоспутников NOAA и обсерватория OAIL — профиль атмосферных и планетных наук, сотрудничество с BRIN
-• Руководитель International Office не установлен</t>
+• Руководитель International Office не установлен
+• Перепроверка: Сайт itera.ac.id и все поддомены по-прежнему 403 (Cloudflare); контакты (pusat@itera.ac.id, тел.) повторно совпадают в выдаче официальных страниц, добавлен humas@itera.ac.id; ректор — по официальной новости ITB (2026)</t>
         </is>
       </c>
       <c r="AG7" s="4" t="inlineStr">
@@ -2690,7 +2692,8 @@
           <t>• ВНИМАНИЕ: домен surya.ac.id сейчас (окт. 2026) показывает сайт «Surya Academy» (математика, бизнес, экономика) без контактов и руководства; старые страницы Surya University (в т.ч. о SS-1) дают 404 — статус вуза (ребрендинг/реорганизация) неясен
 • Ректор не подтверждён официальным источником 2025–2026; в Википедии указаны Lindawati, Ph.D. (id.wiki) и Prof. Yohanes Surya (en.wiki) — перед рассылкой уточнить
 • SS-1 (1U, APRS) — первый студенческий спутник Индонезии: запуск 26.11.2022 (SpaceX CRS-26 к МКС), отделение от МКС 06.01.2023 по программе KiboCUBE, сошёл с орбиты 11.05.2023
-• Email/телефон на текущем сайте не опубликованы — нужен поиск контакта (например, через команду SS-1 или фонд Surya Institute)</t>
+• Email/телефон на текущем сайте не опубликованы — нужен поиск контакта (например, через команду SS-1 или фонд Surya Institute)
+• Перепроверка: Сайт surya.ac.id повторно проверен 04.10.2026: это «Surya Academy» без руководства и контактов; данные не изменены, статус вуза не прояснён</t>
         </is>
       </c>
       <c r="AG5" s="4" t="inlineStr">
@@ -3350,11 +3353,12 @@
       </c>
       <c r="AF9" s="4" t="inlineStr">
         <is>
-          <t>• Сайт itera.ac.id и поддомены блокируют доступ (403 / Cloudflare-проверка) — контакты (pusat@itera.ac.id, iio@itera.ac.id, телефон) взяты только из поисковой выдачи, не со страницы; перепроверить
-• Ректор проф. Эльфахми избран 20.05.2026, вступил в должность 30.06.2026 (срок 2026–2030), сменив проф. I Nyoman Pugeg Aryantha
+          <t>• Сайт itera.ac.id и поддомены (pmb., kemahasiswaan., at., mfi.) блокируют доступ (403 / Cloudflare, повторно 04.10.2026) — контакты (pusat@itera.ac.id, iio@itera.ac.id, +62 721 8030188; PR-служба humas@itera.ac.id) взяты из поисковой выдачи официальных страниц, не открыты; перепроверить
+• Ректор проф. Эльфахми избран 20.05.2026, вступил в должность 30.06.2026 (срок 2026–2030), сменив проф. I Nyoman Pugeg Aryantha — по официальной новости ITB
 • Город: кампус в округе Южный Лампунг рядом с Бандар-Лампунгом
 • Собственных спутников нет; есть станция приёма метеоспутников NOAA и обсерватория OAIL — профиль атмосферных и планетных наук, сотрудничество с BRIN
-• Руководитель International Office не установлен</t>
+• Руководитель International Office не установлен
+• Перепроверка: Сайт itera.ac.id и все поддомены по-прежнему 403 (Cloudflare); контакты (pusat@itera.ac.id, тел.) повторно совпадают в выдаче официальных страниц, добавлен humas@itera.ac.id; ректор — по официальной новости ITB (2026)</t>
         </is>
       </c>
       <c r="AG9" s="4" t="inlineStr">
@@ -5884,10 +5888,25 @@
           <t>Jl. Dr. Setiabudhi No. 229, Bandung 40154, West Java, Indonesia</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>sekuniv_upi@upi.edu</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Директор по международным делам
+Дирекция международных дел (Direktorat Urusan Internasional UPI)
+Обращение: Dear Director of International Affairs,</t>
+        </is>
+      </c>
       <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>sekuniv_upi@upi.edu</t>
+        </is>
+      </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
           <t>+62 22 2013163</t>
@@ -5936,18 +5955,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE26" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF26" s="4" t="inlineStr">
         <is>
-          <t>• Все сайты upi.edu (включая dia.upi.edu — Дирекция международных дел) закрыты Cloudflare-проверкой — email не удалось проверить
-• Адрес и телефон — из вторичных источников (ZoomInfo); по тем же данным директор по международным делам — Ahmad Muslim (не подтверждено официальным сайтом)
+          <t>• Сайт Дирекции международных дел (dia.upi.edu) закрыт Cloudflare-проверкой — международный e-mail не найден; используем общий адрес секретариата sekuniv_upi@upi.edu (с главной страницы upi.edu)
+• Телефон — из вторичных источников (ZoomInfo), на официальном сайте не найден; по тем же данным директор по международным делам — Ahmad Muslim (не подтверждено). Партнёрства курирует проректор по исследованиям, общественной деятельности и партнёрству проф. Agus Setiabudi
 • Ректор Prof. Didi Sukyadi вступил в должность 16.06.2025 (2025–2030)
-• Педагогический университет; космических проектов не найдено (проверка по nanosats.csv)</t>
+• Педагогический университет; космических проектов не найдено (проверка по nanosats.csv)
+• Перепроверка: Ректор проф. Didi Sukyadi, адрес и общий e-mail sekuniv_upi@upi.edu (секретариат университета) подтверждены на upi.edu 04.10.2026; dia.upi.edu по-прежнему закрыт Cloudflare</t>
         </is>
       </c>
       <c r="AG26" s="4" t="inlineStr">
@@ -5956,7 +5980,8 @@
 • Https://dia.upi.edu/
 • Https://www.antaranews.com/berita/4835437/didi-sukyadi-terpilih-sebagai-rektor-upi-2025-2030
 • Https://www.pikiran-rakyat.com/pendidikan/pr-019422008/selamat-didi-sukyadi-resmi-dilantik-menjadi-rektor-upi-periode-2025-2030
-• Https://www.zoominfo.com/pic/universitas-pendidikan-indonesia/442814079</t>
+• Https://www.zoominfo.com/pic/universitas-pendidikan-indonesia/442814079
+• Https://upi.edu/id/rektorat</t>
         </is>
       </c>
       <c r="AH26" s="4" t="inlineStr">
@@ -6331,10 +6356,14 @@
           <t>oia@unsri.ac.id</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>bapsi@unsri.ac.id</t>
+        </is>
+      </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>+62 812 7194 4555</t>
+          <t>+62 711 580169 (общий, PDDikti); +62 812 7194 4555 (OIA, моб.)</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -6388,16 +6417,18 @@
       </c>
       <c r="AF29" s="4" t="inlineStr">
         <is>
-          <t>• Сайт unsri.ac.id закрыт WAF (SafeLine, HTTP 468) — данные из вторичных источников (Wikipedia, AIMS/SEAMEO RIHED)
+          <t>• Сайт unsri.ac.id закрыт WAF (SafeLine, HTTP 468) — данные из вторичных источников и госреестра PDDikti
+• Адрес (Jl. Raya Palembang–Prabumulih Km. 32, Indralaya, 30662), e-mail bapsi@unsri.ac.id и тел. 0711-580169 / факс 0711-580664 — по реестру PDDikti (Минвысшобразования Индонезии); bapsi — информационный отдел, не международный
 • Ректор Prof. Taufiq Marwa — срок 2023–2027 (по поисковой выдаче, инаугурация 25.09.2023); официальная страница не открыта
 • Международный офис: Cooperation and International Services (OIA), Gedung Rektorat 1 этаж; руководитель Sabaruddin, Ph.D. по странице AIMS (дата не указана — проверить); телефон +62 812 7194 4555 — мобильный этого же контакта
-• Общий e-mail не подтверждён (в поисковой выдаче humas@unsri.ac.id, тел. +62 711 580739/580740 — не проверено)
-• Космической активности не обнаружено; отдельная веб-проверка не выполнена (исчерпан лимит поиска), в nanosats.csv вуз отсутствует</t>
+• Космической активности не обнаружено; отдельная веб-проверка не выполнена (исчерпан лимит поиска), в nanosats.csv вуз отсутствует
+• Перепроверка: Сайт unsri.ac.id по-прежнему закрыт WAF (HTTP 468); по госреестру PDDikti подтверждены адрес и индекс, добавлены e-mail bapsi@unsri.ac.id и тел. 0711-580169; ректор и OIA официально не подтверждены</t>
         </is>
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Sriwijaya_University
+          <t>• Https://api-pddikti.kemdiktisaintek.go.id/pt/detail/ (PDDikti, Минвысшобразования Индонезии, код вуза 001009)
+• Https://en.wikipedia.org/wiki/Sriwijaya_University
 • Https://aims-rihed.net/universitas-sriwijaya/</t>
         </is>
       </c>
@@ -7733,7 +7764,8 @@
 • Офис OCIA переименован в Directorate of Global Partnership and Employability (DGPE); по сниппету поиска общий ящик — bkln@umy.ac.id (страницу открыть не удалось) — проверить
 • Директор Fitri Arofiati, Ph.D. указан по данным 2023–2024 — подтвердить актуальность; общий email ректората не найден
 • Ректор Prof. Achmad Nurmandi вступил в должность 30.12.2024 (2024–2028)
-• Космических проектов не найдено (проверка по nanosats.csv)</t>
+• Космических проектов не найдено (проверка по nanosats.csv)
+• Перепроверка: umy.ac.id и partnership.umy.ac.id показывают проверку «Verifying you are human», поддомены dgpe./iro./international. недоступны (прокси 502) — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG38" s="4" t="inlineStr">
@@ -10065,10 +10097,14 @@
           <t>https://www.polban.ac.id</t>
         </is>
       </c>
-      <c r="P54" s="4" t="inlineStr"/>
+      <c r="P54" s="4" t="inlineStr">
+        <is>
+          <t>Marwansyah, S.E., M.Sc., Ph.D.</t>
+        </is>
+      </c>
       <c r="Q54" s="4" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Director (Direktur)</t>
         </is>
       </c>
       <c r="R54" s="4" t="inlineStr"/>
@@ -10098,16 +10134,19 @@
       </c>
       <c r="AE54" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF54" s="4" t="inlineStr">
         <is>
-          <t>• Политехникум возглавляет Директор (Direktur), а не ректор; имя директора на сайте не извлечено (страница 'Pejabat Struktural' без текста) — уточнить вручную
-• Международный офис: Kantor Urusan Internasional (KUI), kui@polban.ac.id; руководитель не найден
+          <t>• Международный офис: Kantor Urusan Internasional (KUI), kui@polban.ac.id; руководитель не найден
 • Инженерный профиль (машиностроение, электротехника/телекоммуникации) — потенциально интересный технический партнёр
 • Не в рейтингах QS/THE 2027; факс +62 22 2013889
-• Космической активности не обнаружено; отдельная веб-проверка не выполнена (исчерпан лимит поиска), в nanosats.csv вуз отсутствует</t>
+• Космической активности не обнаружено; отдельная веб-проверка не выполнена (исчерпан лимит поиска), в nanosats.csv вуз отсутствует
+• Директор — Marwansyah, S.E., M.Sc., Ph.D. (официальный PDF «Pejabat Struktural 2023–2026»); идут выборы директора на 2026–2030, вступление нового директора в должность запланировано на 27.10.2026 — после этой даты перепроверить имя
+• Международные связи курирует Wakil Direktur по планированию, сотрудничеству и ИС — Dr. Ir. Paula Santi Rudati, M.Si. (по PDF 2023–2026)
+• Контакты на главной странице (04.10.2026): polban@polban.ac.id, kui@polban.ac.id, тел. 022-2013789 / 022-2015271, факс 022-2013889
+• Перепроверка: Сайт открылся 04.10.2026: контакты и KUI подтверждены; директор Marwansyah установлен по официальному PDF 2023–2026 (смена директора 27.10.2026)</t>
         </is>
       </c>
       <c r="AG54" s="4" t="inlineStr">
@@ -10115,7 +10154,11 @@
           <t>• Https://www.polban.ac.id/
 • Https://www.polban.ac.id/hubungi-kami/
 • Https://www.polban.ac.id/profil/
-• Https://www.polban.ac.id/pejabat-struktural/</t>
+• Https://www.polban.ac.id/pejabat-struktural/
+• Https://www.polban.ac.id/en/home/
+• Https://www.polban.ac.id/wp-content/uploads/2023/02/pejabat-struktural-polban-2023-2026-3.pdf
+• Https://www.polban.ac.id/polban-selenggarakan-pemilihan-direktur-masa-bakti-2026-2030/
+• Https://pildir.polban.ac.id/</t>
         </is>
       </c>
       <c r="AH54" s="4" t="inlineStr">
@@ -10463,9 +10506,10 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
+          <t>Prof. Dr. I Wayan Lasmawan, M.Pd.
+Rector, Universitas Pendidikan Ganesha
 Бюро по связям с общественностью (Humas Undiksha)
-Обращение: Dear Rector,</t>
+Обращение: Dear Professor Lasmawan,</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr"/>
@@ -10484,10 +10528,14 @@
           <t>https://undiksha.ac.id</t>
         </is>
       </c>
-      <c r="P57" s="4" t="inlineStr"/>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Dr. I Wayan Lasmawan, M.Pd.</t>
+        </is>
+      </c>
       <c r="Q57" s="4" t="inlineStr">
         <is>
-          <t>Rector</t>
+          <t>Rector (Rektor)</t>
         </is>
       </c>
       <c r="R57" s="4" t="inlineStr"/>
@@ -10517,21 +10565,21 @@
       </c>
       <c r="AE57" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF57" s="4" t="inlineStr">
         <is>
-          <t>• Основной сайт undiksha.ac.id закрыт Cloudflare-проверкой; контакты взяты с сайта LPPM Undiksha (подвал сайта университета)
-• Ректор не подтверждён официальным источником: в id.wikipedia — Prof. Dr. I Wayan Lasmawan, M.Pd., в en.wikipedia — устаревшее имя (Prof. I Nyoman Jampel) — уточнить перед рассылкой
+          <t>• Основной сайт undiksha.ac.id закрыт Cloudflare-проверкой; ректор, адрес, телефон (0362) 22570 и humas@undiksha.ac.id подтверждены на официальном портале PPID Undiksha (новости от 3.10.2026)
 • Humas@ — пресс-служба; email международного офиса не найден
 • Космических проектов не найдено (проверка по nanosats.csv)
-• THE2027: только статус Reporter (без ранга)</t>
+• THE2027: только статус Reporter (без ранга)
+• Перепроверка: 04.10.2026: ректор проф. И Ваян Ласмаван, адрес, телефон и e-mail подтверждены на официальном портале ppid.undiksha.ac.id</t>
         </is>
       </c>
       <c r="AG57" s="4" t="inlineStr">
         <is>
-          <t>• Https://undiksha.ac.id/
+          <t>• Https://ppid.undiksha.ac.id/
 • Https://lppm.undiksha.ac.id/
 • Https://lppm.undiksha.ac.id/hubungi-kami/
 • Https://id.wikipedia.org/wiki/Universitas_Pendidikan_Ganesha</t>
@@ -11513,7 +11561,8 @@
 • Международный офис (OIA, возобновлён в 2025) имеет сайт international.ulm.ac.id, но e-mail скрыт защитой; тел./факс офиса +62 511 3304177 / 3305195 — из выдачи
 • Общий e-mail humas@ulm.ac.id — отдел по связям с общественностью
 • Спутники: в базе nanosats ничего нет
-• Новый ректор: Dr. Iwan Aflanie (избран 02.10.2026, вступление ~05.10.2026) — адресовать письмо ему</t>
+• Новый ректор: Dr. Iwan Aflanie (избран 02.10.2026, вступление ~05.10.2026) — адресовать письмо ему
+• Перепроверка: ulm.ac.id и international.ulm.ac.id по-прежнему закрыты Cloudflare 403 — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG64" s="4" t="inlineStr">
@@ -11790,7 +11839,9 @@
 • Сайт umj.ac.id и поддомены закрыты Cloudflare / недоступны — контакты не проверены; единственный найденный e-mail pmb@umj.ac.id — приёмная комиссия (не для официальной переписки)
 • Ректор Ma'mun Murod назначен в 2021 г. на срок 2021–2025 (Wikipedia); актуальность на 2026 г. не подтверждена
 • Кампус A: Jl. Cempaka Putih Tengah 27, Jakarta 10510
-• Космической активности не обнаружено; отдельная веб-проверка не выполнена (исчерпан лимит поиска), в nanosats.csv вуз отсутствует</t>
+• Космической активности не обнаружено; отдельная веб-проверка не выполнена (исчерпан лимит поиска), в nanosats.csv вуз отсутствует
+• Ректор Prof. Dr. Ma'mun Murod переизбран и вступил в должность 26.05.2025 на срок 2025–2029 (Suara Muhammadiyah — официальное издание организации-учредителя, 27.05.2025)
+• Перепроверка: 04.10.2026: ректор подтверждён на 2025–2029 (Suara Muhammadiyah); сайт umj.ac.id по-прежнему закрыт (403) — контакты не подтверждены</t>
         </is>
       </c>
       <c r="AG66" s="4" t="inlineStr">
@@ -12000,13 +12051,27 @@
           <t>Jl. Kapt. Mukhtar Basri No. 3, Medan, North Sumatra 20238, Indonesia</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr"/>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>kui@umsu.ac.id</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Lembaga Kerjasama dan Urusan Internasional UMSU (OIC)
+Обращение: Dear Director of the Office of International Affairs,</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>kui@umsu.ac.id</t>
+        </is>
+      </c>
       <c r="M68" s="4" t="inlineStr"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>+62 61 6619056</t>
+          <t>+62 61 6619056; +62 61 6622400 ext. 106/108; international office +62 811-6516-817</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
@@ -12048,18 +12113,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD68" s="4" t="inlineStr"/>
+      <c r="AD68" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE68" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF68" s="4" t="inlineStr">
         <is>
-          <t>• Частный университет организации Мухаммадия; ректор проф. Акрим (фото на странице руководства загружено в 2026 г.)
-• На официальном сайте не опубликован ни общий, ни международный e-mail — только телефоны (+62 61 6619056; +62 61 6622400 доб. 106/108); нужно запросить адрес по телефону или через соцсети
-• Международные связи: Lembaga Kerjasama dan Urusan Internasional (oic.umsu.ac.id) и Biro Kerja Sama dan Kemitraan Strategis (partnership.umsu.ac.id); руководители не указаны
-• Спутниковых проектов нет (nanosats.csv)</t>
+          <t>• Частный университет организации Мухаммадия
+• Общий e-mail на сайте не опубликован; международный офис (Lembaga Kerjasama dan Urusan Internasional, oic.umsu.ac.id): kui@umsu.ac.id, +62 811-6516-817
+• Международные связи курирует проректор по исследованиям, инновациям и интернационализации Dr. Rudianto, S.Sos., M.Si; руководитель OIC на сайте не указан
+• Спутниковых проектов нет (nanosats.csv)
+• Перепроверка: Ректор проф. Акрим подтверждён (стр. руководства и новости 09.2026); найден e-mail международного офиса kui@umsu.ac.id на oic.umsu.ac.id, 04.10.2026</t>
         </is>
       </c>
       <c r="AG68" s="4" t="inlineStr">
@@ -12067,7 +12137,8 @@
           <t>• Https://umsu.ac.id/
 • Https://umsu.ac.id/pimpinan/
 • Https://oic.umsu.ac.id/
-• Https://partnership.umsu.ac.id/</t>
+• Https://partnership.umsu.ac.id/
+• Https://oic.umsu.ac.id/struktur-organisasi/</t>
         </is>
       </c>
       <c r="AH68" s="4" t="inlineStr">
@@ -14456,10 +14527,10 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
-Руководитель отдела сотрудничества
-Отдел сотрудничества UNM (Kerjasama UNM)
-Обращение: Dear Head of the Partnership Office,</t>
+          <t>Prof. Dr. Syahruddin, M.Kes.
+Vice-Rector IV for Planning and Cooperation (Wakil Rektor IV Bidang Perencanaan dan Kerja Sama)
+Biro Perencanaan dan Kerja Sama UNM (Bureau of Planning and Cooperation)
+Обращение: Dear Prof. Syahruddin,</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -14507,21 +14578,24 @@
       </c>
       <c r="AE85" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF85" s="4" t="inlineStr">
         <is>
           <t>• Основной сайт unm.ac.id и большинство поддоменов закрыты Cloudflare-проверкой; доступен только портал сотрудничества kerjasama.unm.ac.id (ящик kerjasama@unm.ac.id, также ящики факультетов, напр. kerjasama.ft@unm.ac.id, kerjasama.fmipa@unm.ac.id)
-• Руководство нестабильно: по id.wikipedia обязанности ректора исполняет (Plt.) Prof. Dr. Farida Patittingi, S.H., M.Hum. — официально не подтверждено, проверить перед рассылкой
-• Телефон и общий email не подтверждены
-• Космических проектов не найдено (проверка по nanosats.csv)</t>
+• Команда сотрудничества (страница «Tentang»): Wakil Rektor IV — Prof. Dr. Syahruddin, M.Kes.; Kepala Biro Perencanaan dan Kerjasama — Mufti Muin Ismail, M.Pd.; координатор международного сотрудничества — Bukhari Naufal Nur A G, S.Kom
+• Руководство нестабильно: по id.wikipedia обязанности ректора исполняет (Plt.) Prof. Dr. Farida Patittingi, S.H., M.Hum. — на официальных страницах не подтверждено (в новостях 2025 г. упоминается лишь «Rektor UNM» без имени), проверить перед рассылкой
+• Телефон и общий email не подтверждены; адрес — по Википедии
+• Космических проектов не найдено (проверка по nanosats.csv)
+• Перепроверка: 04.10.2026: на портале kerjasama.unm.ac.id подтверждены kerjasama@unm.ac.id, проректор IV по планированию и сотрудничеству Prof. Dr. Syahruddin и руководитель бюро (новости дек. 2025); ректор на доступных официальных страницах не назван, основной сайт закрыт Cloudflare</t>
         </is>
       </c>
       <c r="AG85" s="4" t="inlineStr">
         <is>
-          <t>• Https://unm.ac.id/
-• Https://kerjasama.unm.ac.id/
+          <t>• Https://kerjasama.unm.ac.id/
+• Https://kerjasama.unm.ac.id/tentang
+• Http://kerjasama.unm.ac.id/articles/unm-terima-kunjungan-delegasi-uin-jakarta-bahas-tata-kelola-kerja-sama-kemitraan-internasional-dan-pengelolaan-dana-kolaborasi
 • Https://id.wikipedia.org/wiki/Universitas_Negeri_Makassar</t>
         </is>
       </c>
@@ -15570,7 +15644,7 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>Jl. Limau II, Kebayoran Baru, South Jakarta, DKI Jakarta, Indonesia</t>
+          <t>Jl. Limau II, Kebayoran Baru, Jakarta Selatan, DKI Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -15593,7 +15667,7 @@
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>+62 858 1300 1400</t>
+          <t>+62 821 8000 1957 (Humas); +62 858 1300 1400 (PMB)</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
@@ -15638,15 +15712,16 @@
       </c>
       <c r="AE93" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF93" s="4" t="inlineStr">
         <is>
           <t>• THE2027: только статус Reporter (без ранга)
-• Основной сайт uhamka.ac.id — SPA, международный офис (kui/oia.uhamka.ac.id) закрыт Cloudflare; e-mail humas@uhamka.ac.id и тел. +62 858 1300 1400 — со страницы приёмной комиссии
+• Основной сайт uhamka.ac.id — SPA; данные (в т.ч. имя ректора) подгружаются с API uhamka-baru-be.uhamka.ac.id, закрытого Cloudflare; международный офис (kui/oia.uhamka.ac.id) недоступен/закрыт Cloudflare. На сайте также указан info@uhamka.ac.id
 • Ректор Gunawan Suryoputro (с 2018 г.) — только по Wikipedia, актуальность на 2026 г. не подтверждена
-• Космической активности не обнаружено; отдельная веб-проверка не выполнена (исчерпан лимит поиска), в nanosats.csv вуз отсутствует</t>
+• Космической активности не обнаружено; отдельная веб-проверка не выполнена (исчерпан лимит поиска), в nanosats.csv вуз отсутствует
+• Перепроверка: Адрес, humas@uhamka.ac.id и телефоны Humas/PMB подтверждены на uhamka.ac.id (страница «Sambutan Rektor») 04.10.2026; имя ректора не отображается (API сайта закрыт Cloudflare) — не подтверждено</t>
         </is>
       </c>
       <c r="AG93" s="4" t="inlineStr">
@@ -17353,10 +17428,11 @@
       </c>
       <c r="AF105" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт www.unja.ac.id закрыт проверкой Cloudflare (403 / «Just a moment…»), сайт International Office internationaloffice.unja.ac.id — хостинг приостановлен (account suspended); контакты со страниц подтвердить не удалось — поля оставлены пустыми
-• Ректор Prof. Dr. Helmi, S.H., M.H. (срок 2024–2028) — только по Wikipedia (EN/ID), не с официального сайта
+          <t>• Официальный сайт www.unja.ac.id и поддомены (ppid., humas., lppm.) по-прежнему закрыты Cloudflare (403); internationaloffice.unja.ac.id — хостинг приостановлен (account suspended) — контакты со страниц подтвердить не удалось, поля оставлены пустыми
+• Ректор Prof. Dr. Helmi, S.H., M.H. (9-й ректор, вступил в должность 31.01.2024, срок 2024–2028) — подтверждён госагентством ANTARA и региональными СМИ 2026 г. (назначения должностных лиц 06–08.2026); на официальном сайте не проверен
 • Неподтверждённые данные из поисковых сниппетов: адрес Jl. Jambi – Muara Bulian KM 15, Mendalo Darat, Jambi Luar Kota, Muaro Jambi 36361; тел. +62 741 583122 / 583377; humas@unja.ac.id; International Office — io@unja.ac.id (здание ректората, 2 этаж, кампус Mendalo) — проверить перед отправкой
-• Спутниковых проектов не найдено (nanosats.csv)</t>
+• Спутниковых проектов не найдено (nanosats.csv)
+• Перепроверка: Сайт закрыт Cloudflare; ректор подтверждён СМИ 2026 г. (ANTARA), контакты не изменены</t>
         </is>
       </c>
       <c r="AG105" s="4" t="inlineStr">
@@ -18197,7 +18273,9 @@
           <t>• Все сайты Widyatama (включая kerma.widyatama.ac.id) закрыты Cloudflare (403) — данные взяты из поисковой выдачи, страницы открыть не удалось
 • Ректор проф. Даданг Суганда подтверждается несколькими публикациями 2026 г.; ранее в СМИ сообщалось о внутреннем конфликте и отставке прежнего ректора
 • Международными связями ведает Kerma (отдел сотрудничества), e-mail не найден; общий адрес — секретарь университета
-• Спутники: в базе nanosats ничего нет</t>
+• Спутники: в базе nanosats ничего нет
+• По поисковому сниппету страницы kerma.widyatama.ac.id/about: бюро сотрудничества Kerma (с 2016) — тел. +62 22 7275855 доб. 129 (не открыто, 04.10.2026)
+• Перепроверка: Сайты Widyatama по-прежнему за Cloudflare (403); добавлен по выдаче телефон отдела Kerma (доб. 129); e-mail не найден</t>
         </is>
       </c>
       <c r="AG111" s="4" t="inlineStr">
